--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2020_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2020_biobio.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:11</t>
+    <t xml:space="preserve">2026-09-24 01:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>-0.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.26</v>
@@ -704,13 +704,13 @@
         <v>26</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +730,7 @@
         <v>-0.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.11</v>
@@ -753,10 +753,10 @@
         <v>-0.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
